--- a/public/downloads/helix-metrics-tracker.xlsx
+++ b/public/downloads/helix-metrics-tracker.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start here" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Start here" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Daily" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Total sales for the day, before GST/VAT if you are registered</t>
+          <t>Net sales for the day (after discounts and returns, no shipping), before GST/VAT if you are registered</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">

--- a/public/downloads/helix-metrics-tracker.xlsx
+++ b/public/downloads/helix-metrics-tracker.xlsx
@@ -577,7 +577,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Google Sheets: File &gt; Import &gt; Upload this file. Excel and Numbers open it directly.</t>
+          <t>Any spreadsheet app opens this file. In an online spreadsheet, use File &gt; Import &gt; Upload.</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>Shopify Payments, PayPal and so on</t>
+          <t>Shopify Payments and other payment providers</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
